--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46063.5315739623</v>
+        <v>46065.67708170296</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="6"/>
@@ -10916,7 +10916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:EL3"/>
+  <dimension ref="A1:EL75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="6">
@@ -13053,6 +13053,2454 @@
         <is>
           <t>org_nitro_unit</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESL079</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESL078</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV5" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESL077</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV6" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESL076</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ESL075</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV8" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESL074</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ESL073</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV10" t="n">
+        <v>124</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>124</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESL072</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV11" t="n">
+        <v>176</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>176</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ESL071</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV12" t="n">
+        <v>210</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>210</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ESL069</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV13" t="n">
+        <v>258</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>258</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ESL068</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV14" t="n">
+        <v>280</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>280</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ESL067</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ESL066</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV16" t="n">
+        <v>308</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>308</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ESL065</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV17" t="n">
+        <v>322</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>322</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ESL064</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV18" t="n">
+        <v>330</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>330</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ESL063</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV19" t="n">
+        <v>340</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>340</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ESL062</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV20" t="n">
+        <v>346</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>346</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ESL061</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV21" t="n">
+        <v>356</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>356</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ESL059</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV22" t="n">
+        <v>368</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>368</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ESL058</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV23" t="n">
+        <v>380</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>380</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ESL057</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV24" t="n">
+        <v>419</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>419</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ESL056</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV25" t="n">
+        <v>457</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>457</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ESL055</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV26" t="n">
+        <v>467</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>467</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ESL054</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV27" t="n">
+        <v>479</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>479</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ESL053</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV28" t="n">
+        <v>491</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>491</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ESL052</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV29" t="n">
+        <v>507</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>507</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ESL051</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV30" t="n">
+        <v>547</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>547</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ESL049</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV31" t="n">
+        <v>566</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>566</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ESL048</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV32" t="n">
+        <v>590</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>590</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ESL047</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV33" t="n">
+        <v>635</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>635</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ESL046</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV34" t="n">
+        <v>670</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>670</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ESL045</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV35" t="n">
+        <v>717</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>717</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ESL044</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV36" t="n">
+        <v>728</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>728</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ESL043</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV37" t="n">
+        <v>739</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>739</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ESL042</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV38" t="n">
+        <v>758</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>758</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ESL041</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV39" t="n">
+        <v>784</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>784</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ESL039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV40" t="n">
+        <v>805</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>805</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ESL038</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV41" t="n">
+        <v>821</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>821</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ESL037</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV42" t="n">
+        <v>829</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>829</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ESL036</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV43" t="n">
+        <v>841</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>841</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ESL035</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV44" t="n">
+        <v>850</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>850</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ESL034</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV45" t="n">
+        <v>860</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>860</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ESL033</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV46" t="n">
+        <v>870</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>870</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ESL032</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV47" t="n">
+        <v>878</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>878</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ESL031</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV48" t="n">
+        <v>895</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>895</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ESL029</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV49" t="n">
+        <v>905</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>905</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ESL028</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV50" t="n">
+        <v>917</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>917</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ESL027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV51" t="n">
+        <v>934</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>934</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ESL026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV52" t="n">
+        <v>973</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>973</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ESL025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV53" t="n">
+        <v>993</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>993</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ESL024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV54" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ESL023</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV55" t="n">
+        <v>1053</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>1053</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ESL022</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV56" t="n">
+        <v>1085</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>1085</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ESL021</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV57" t="n">
+        <v>1113</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1113</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ESL019</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV58" t="n">
+        <v>1172</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1172</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ESL018</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV59" t="n">
+        <v>1201</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>1201</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ESL017</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV60" t="n">
+        <v>1235</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>1235</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ESL016</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV61" t="n">
+        <v>1252</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>1252</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ESL015</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV62" t="n">
+        <v>1282</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>1282</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ESL014</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV63" t="n">
+        <v>1315</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>1315</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ESL013</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV64" t="n">
+        <v>1351</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>1351</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ESL012</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV65" t="n">
+        <v>1379</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>1379</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ESL011</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV66" t="n">
+        <v>1415</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>1415</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ESL009</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV67" t="n">
+        <v>1463</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>1463</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ESL008</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV68" t="n">
+        <v>1534</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>1534</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ESL007</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV69" t="n">
+        <v>1622</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>1622</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ESL006</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV70" t="n">
+        <v>1648</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>1648</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ESL005</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV71" t="n">
+        <v>1672</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>1672</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ESL004</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV72" t="n">
+        <v>1692</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>1692</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ESL003</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV73" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ESL002</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV74" t="n">
+        <v>1762</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>1762</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ESL001</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>China; Sichuan</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Niederreiter piston corer</t>
+        </is>
+      </c>
+      <c r="BV75" t="n">
+        <v>1777</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>1777</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>4165</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,9 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -138,7 +136,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -159,9 +157,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3824,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="6">
@@ -3842,70 +3837,56 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="6">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Modified by:</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Date/Time generated;</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="6">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>neotoma2FAIRe v0.1.0</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2025-07-02T11:34:09+08:00</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="6">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Date/Time generated;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46065.67708170296</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="6"/>
+          <t>Note: This template includes all data components and terms from the FAIR eDNA checklist, encompassing sections for both targeted assays and metabarcoding assay types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Requirement levels;</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="15" customHeight="1" s="6">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Note: This template includes all data components and terms from the FAIR eDNA checklist, encompassing sections for both targeted assays and metabarcoding assay types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="6"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>M = Mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="6">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>HR = Highly recommended</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="15" customHeight="1" s="6">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Requirement levels;</t>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>R = Recommended</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="6">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>M = Mandatory</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>HR = Highly recommended</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>R = Recommended</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>O = Optional</t>
         </is>
@@ -3933,102 +3914,102 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4142,107 +4123,107 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>seq_id</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>dna_sequence</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>kingdom</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>phylum</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>family</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>genus</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>specificEpithet</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>scientificName</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>scientificNameAuthorship</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>taxonRank</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>taxonID</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>taxonID_db</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>verbatimIdentification</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>accession_id</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>accession_id_ref_db</t>
         </is>
       </c>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr">
         <is>
           <t>percent_match</t>
         </is>
       </c>
-      <c r="S3" s="13" t="inlineStr">
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>percent_query_cover</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>confidence_score</t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr">
         <is>
           <t>identificationRemarks</t>
         </is>
@@ -4272,29 +4253,29 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="6">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>term_name</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>project_level</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="6">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4304,14 +4285,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>recordedBy</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4321,14 +4302,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>recordedByID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="6">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4338,14 +4319,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>project_contact</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="6">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4355,19 +4336,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>institution</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AHAHA</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4377,19 +4353,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>institutionID</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AHAHA</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="6">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4399,14 +4370,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>project_name</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="6">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4416,14 +4387,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>project_id</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="6">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4433,14 +4404,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>parent_project_id</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="6">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4450,14 +4421,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>study_factor</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="6">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4467,14 +4438,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>assay_type</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="6">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4484,14 +4455,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>sterilise_method</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="6">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4501,14 +4472,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>neg_cont_0_1</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="6">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4518,14 +4489,14 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>pos_cont_0_1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="6">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4535,14 +4506,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>checkls_ver</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="6">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4552,14 +4523,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>mod_date</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="6">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4569,14 +4540,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>license</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="6">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4586,14 +4557,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>rightsHolder</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="6">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4603,14 +4574,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>accessRights</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="6">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4620,14 +4591,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>informationWithheld</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="6">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4637,14 +4608,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>dataGeneralizations</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="6">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4654,14 +4625,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>bibliographicCitation</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="6">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4671,14 +4642,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="6">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4688,14 +4659,14 @@
           <t>Data management</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>code_repo</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="6">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4705,14 +4676,14 @@
           <t>Sample collection</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>biological_rep</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="6">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4722,14 +4693,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>pcr_0_1</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="6">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4739,14 +4710,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>inhibition_check_0_1</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="6">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4756,14 +4727,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>inhibition_check</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="6">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4773,14 +4744,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>thermocycler</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="6">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4790,14 +4761,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="6">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4807,14 +4778,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>assay_validation</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="6">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4824,14 +4795,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>targetTaxonomicAssay</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="6">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4841,14 +4812,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>targetTaxonomicScope</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="6">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4858,14 +4829,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>target_gene</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="6">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4875,14 +4846,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>target_subfragment</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="6">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4892,14 +4863,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>ampliconSize</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="6">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4909,14 +4880,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_forward</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="6">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4926,14 +4897,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_reverse</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="6">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4943,14 +4914,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_name_forward</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="6">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4960,14 +4931,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_name_reverse</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="6">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4977,14 +4948,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_reference_forward</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="6">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -4994,14 +4965,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_reference_reverse</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="6">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5011,14 +4982,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_vol_forward</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="6">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5028,14 +4999,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_vol_reverse</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="6">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5045,14 +5016,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_conc_forward</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="6">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5062,14 +5033,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>pcr_primer_conc_reverse</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="6">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5079,14 +5050,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>probeReporter</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="6">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5096,14 +5067,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>probeQuencher</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="6">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5113,14 +5084,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>probe_seq</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="6">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5130,14 +5101,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>probe_ref</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="6">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5147,14 +5118,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>probe_conc</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="6">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5164,14 +5135,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>commercial_mm</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="6">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5181,14 +5152,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>custom_mm</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="6">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5198,14 +5169,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>block_seq</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="6">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5215,14 +5186,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>block_ref</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="6">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5232,14 +5203,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>block_taxa</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="6">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5249,14 +5220,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>amplificationReactionVolume</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="6">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5266,14 +5237,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>pcr_dna_vol</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="6">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5283,14 +5254,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>pcr_rep</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="6">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5300,14 +5271,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_amp</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="6">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5317,14 +5288,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>pcr_cond</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="6">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5334,14 +5305,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>annealingTemp</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="6">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5351,14 +5322,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>pcr_cycles</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="6">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5368,14 +5339,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>pcr_analysis_software</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="6">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5385,14 +5356,14 @@
           <t>PCR</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>pcr_method_additional</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="6">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5402,14 +5373,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>amp_vis_method</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="6">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5419,14 +5390,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>detection_criteria</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="6">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5436,14 +5407,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>lod_method</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="6">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5453,14 +5424,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_lod_techreps</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="6">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5470,14 +5441,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_lod</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="6">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5487,14 +5458,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_lod_unit</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="6">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5504,14 +5475,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_lod_UL</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="6">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5521,14 +5492,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_lod_LL</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="6">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5538,14 +5509,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>loq_method</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="6">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5555,14 +5526,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_loq_techreps</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="6">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5572,14 +5543,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C76" s="13" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_loq</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="6">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5589,14 +5560,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_loq_unit</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="6">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5606,14 +5577,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C78" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_loq_UL</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="6">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5623,14 +5594,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C79" s="12" t="inlineStr">
         <is>
           <t>pcr_assay_loq_LL</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="6">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5640,14 +5611,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>std_type</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="6">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5657,14 +5628,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C81" s="12" t="inlineStr">
         <is>
           <t>std_source</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="6">
-      <c r="A82" s="11" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5674,14 +5645,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C82" s="12" t="inlineStr">
         <is>
           <t>std_seq</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="6">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5691,14 +5662,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
         <is>
           <t>thresholdQuantificationCycle</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="6">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5708,14 +5679,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>baselineValue</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="6">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5725,14 +5696,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C85" s="12" t="inlineStr">
         <is>
           <t>automaticThresholdQuantificationCycle</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="6">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5742,14 +5713,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C86" s="13" t="inlineStr">
+      <c r="C86" s="12" t="inlineStr">
         <is>
           <t>automaticBaselineValue</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="6">
-      <c r="A87" s="12" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5759,14 +5730,14 @@
           <t>Targeted assay detection</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>targeted_detection_method_additional</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="6">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5776,14 +5747,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C88" s="13" t="inlineStr">
+      <c r="C88" s="12" t="inlineStr">
         <is>
           <t>barcoding_pcr_appr</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="6">
-      <c r="A89" s="12" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5793,14 +5764,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>pcr2_thermocycler</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="6">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5810,14 +5781,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C90" s="13" t="inlineStr">
+      <c r="C90" s="12" t="inlineStr">
         <is>
           <t>pcr2_amplificationReactionVolume</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="6">
-      <c r="A91" s="11" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5827,14 +5798,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C91" s="13" t="inlineStr">
+      <c r="C91" s="12" t="inlineStr">
         <is>
           <t>pcr2_commercial_mm</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="6">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5844,14 +5815,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
         <is>
           <t>pcr2_custom_mm</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="6">
-      <c r="A93" s="11" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5861,14 +5832,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C93" s="12" t="inlineStr">
         <is>
           <t>pcr2_dna_vol</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="6">
-      <c r="A94" s="11" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5878,14 +5849,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C94" s="13" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
         <is>
           <t>pcr2_cond</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="6">
-      <c r="A95" s="11" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5895,14 +5866,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C95" s="13" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
         <is>
           <t>pcr2_annealingTemp</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="6">
-      <c r="A96" s="11" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5912,14 +5883,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C96" s="13" t="inlineStr">
+      <c r="C96" s="12" t="inlineStr">
         <is>
           <t>pcr2_cycles</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="6">
-      <c r="A97" s="12" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5929,14 +5900,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C97" s="13" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>pcr2_analysis_software</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="6">
-      <c r="A98" s="11" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5946,14 +5917,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C98" s="13" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>pcr2_plate_id</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="6">
-      <c r="A99" s="12" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5963,14 +5934,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C99" s="13" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>pcr2_method_additional</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="6">
-      <c r="A100" s="12" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5980,14 +5951,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr">
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>sequencing_location</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="6">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -5997,14 +5968,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C101" s="13" t="inlineStr">
+      <c r="C101" s="12" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="6">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6014,14 +5985,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C102" s="13" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="6">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6031,14 +6002,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C103" s="13" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>seq_kit</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="6">
-      <c r="A104" s="11" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6048,14 +6019,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C104" s="13" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>lib_layout</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="6">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6065,14 +6036,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C105" s="13" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>adapter_forward</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="6">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6082,14 +6053,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C106" s="13" t="inlineStr">
+      <c r="C106" s="12" t="inlineStr">
         <is>
           <t>adapter_reverse</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="6">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6099,14 +6070,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C107" s="13" t="inlineStr">
+      <c r="C107" s="12" t="inlineStr">
         <is>
           <t>lib_screen</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="6">
-      <c r="A108" s="11" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6116,14 +6087,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C108" s="13" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>checksum_method</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="6">
-      <c r="A109" s="12" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -6133,14 +6104,14 @@
           <t>Library preparation sequencing</t>
         </is>
       </c>
-      <c r="C109" s="13" t="inlineStr">
+      <c r="C109" s="12" t="inlineStr">
         <is>
           <t>seq_method_additional</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="6">
-      <c r="A110" s="11" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6150,14 +6121,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C110" s="13" t="inlineStr">
+      <c r="C110" s="12" t="inlineStr">
         <is>
           <t>sop_bioinformatics</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="6">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6167,14 +6138,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C111" s="13" t="inlineStr">
+      <c r="C111" s="12" t="inlineStr">
         <is>
           <t>trim_method</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="6">
-      <c r="A112" s="11" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6184,14 +6155,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C112" s="13" t="inlineStr">
+      <c r="C112" s="12" t="inlineStr">
         <is>
           <t>trim_param</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="6">
-      <c r="A113" s="11" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6201,14 +6172,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
+      <c r="C113" s="12" t="inlineStr">
         <is>
           <t>demux_tool</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="6">
-      <c r="A114" s="11" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6218,14 +6189,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C114" s="13" t="inlineStr">
+      <c r="C114" s="12" t="inlineStr">
         <is>
           <t>demux_max_mismatch</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="6">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6235,14 +6206,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C115" s="13" t="inlineStr">
+      <c r="C115" s="12" t="inlineStr">
         <is>
           <t>merge_tool</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="6">
-      <c r="A116" s="11" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6252,14 +6223,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C116" s="12" t="inlineStr">
         <is>
           <t>merge_min_overlap</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="6">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6269,14 +6240,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C117" s="13" t="inlineStr">
+      <c r="C117" s="12" t="inlineStr">
         <is>
           <t>min_len_cutoff</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="6">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6286,14 +6257,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C118" s="13" t="inlineStr">
+      <c r="C118" s="12" t="inlineStr">
         <is>
           <t>min_len_tool</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="6">
-      <c r="A119" s="11" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6303,14 +6274,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C119" s="13" t="inlineStr">
+      <c r="C119" s="12" t="inlineStr">
         <is>
           <t>error_rate_tool</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="6">
-      <c r="A120" s="11" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6320,14 +6291,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C120" s="13" t="inlineStr">
+      <c r="C120" s="12" t="inlineStr">
         <is>
           <t>error_rate_type</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="6">
-      <c r="A121" s="11" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6337,14 +6308,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C121" s="13" t="inlineStr">
+      <c r="C121" s="12" t="inlineStr">
         <is>
           <t>error_rate_cutoff</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="6">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6354,14 +6325,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C122" s="13" t="inlineStr">
+      <c r="C122" s="12" t="inlineStr">
         <is>
           <t>chimera_check_method</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="6">
-      <c r="A123" s="11" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6371,14 +6342,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C123" s="13" t="inlineStr">
+      <c r="C123" s="12" t="inlineStr">
         <is>
           <t>chimera_check_param</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="6">
-      <c r="A124" s="11" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6388,14 +6359,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C124" s="13" t="inlineStr">
+      <c r="C124" s="12" t="inlineStr">
         <is>
           <t>otu_clust_tool</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="6">
-      <c r="A125" s="11" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6405,14 +6376,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C125" s="13" t="inlineStr">
+      <c r="C125" s="12" t="inlineStr">
         <is>
           <t>otu_clust_cutoff</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="6">
-      <c r="A126" s="11" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6422,14 +6393,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C126" s="13" t="inlineStr">
+      <c r="C126" s="12" t="inlineStr">
         <is>
           <t>min_reads_cutoff</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="6">
-      <c r="A127" s="11" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6439,14 +6410,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C127" s="13" t="inlineStr">
+      <c r="C127" s="12" t="inlineStr">
         <is>
           <t>min_reads_cutoff_unit</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="6">
-      <c r="A128" s="11" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6456,14 +6427,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C128" s="13" t="inlineStr">
+      <c r="C128" s="12" t="inlineStr">
         <is>
           <t>min_reads_tool</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="6">
-      <c r="A129" s="10" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6473,14 +6444,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C129" s="13" t="inlineStr">
+      <c r="C129" s="12" t="inlineStr">
         <is>
           <t>otu_db</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="6">
-      <c r="A130" s="12" t="inlineStr">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -6490,14 +6461,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C130" s="13" t="inlineStr">
+      <c r="C130" s="12" t="inlineStr">
         <is>
           <t>otu_db_custom</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="6">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6507,14 +6478,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C131" s="13" t="inlineStr">
+      <c r="C131" s="12" t="inlineStr">
         <is>
           <t>tax_assign_cat</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="6">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6524,14 +6495,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C132" s="13" t="inlineStr">
+      <c r="C132" s="12" t="inlineStr">
         <is>
           <t>otu_seq_comp_appr</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="6">
-      <c r="A133" s="11" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6541,14 +6512,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C133" s="13" t="inlineStr">
+      <c r="C133" s="12" t="inlineStr">
         <is>
           <t>tax_class_id_cutoff</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="6">
-      <c r="A134" s="11" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6558,14 +6529,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C134" s="13" t="inlineStr">
+      <c r="C134" s="12" t="inlineStr">
         <is>
           <t>tax_class_query_cutoff</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="6">
-      <c r="A135" s="11" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6575,14 +6546,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C135" s="13" t="inlineStr">
+      <c r="C135" s="12" t="inlineStr">
         <is>
           <t>tax_class_collapse</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="6">
-      <c r="A136" s="11" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6592,14 +6563,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C136" s="13" t="inlineStr">
+      <c r="C136" s="12" t="inlineStr">
         <is>
           <t>tax_class_other</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="6">
-      <c r="A137" s="10" t="inlineStr">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -6609,14 +6580,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C137" s="13" t="inlineStr">
+      <c r="C137" s="12" t="inlineStr">
         <is>
           <t>screen_contam_method</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="6">
-      <c r="A138" s="11" t="inlineStr">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6626,14 +6597,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C138" s="13" t="inlineStr">
+      <c r="C138" s="12" t="inlineStr">
         <is>
           <t>screen_geograph_method</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="6">
-      <c r="A139" s="11" t="inlineStr">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6643,14 +6614,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C139" s="13" t="inlineStr">
+      <c r="C139" s="12" t="inlineStr">
         <is>
           <t>screen_nontarget_method</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="6">
-      <c r="A140" s="11" t="inlineStr">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6660,14 +6631,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C140" s="13" t="inlineStr">
+      <c r="C140" s="12" t="inlineStr">
         <is>
           <t>screen_other</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="6">
-      <c r="A141" s="11" t="inlineStr">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6677,14 +6648,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C141" s="13" t="inlineStr">
+      <c r="C141" s="12" t="inlineStr">
         <is>
           <t>otu_raw_description</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="6">
-      <c r="A142" s="11" t="inlineStr">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6694,14 +6665,14 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C142" s="13" t="inlineStr">
+      <c r="C142" s="12" t="inlineStr">
         <is>
           <t>otu_final_description</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="6">
-      <c r="A143" s="12" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -6711,7 +6682,7 @@
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="C143" s="13" t="inlineStr">
+      <c r="C143" s="12" t="inlineStr">
         <is>
           <t>bioinfo_method_additional</t>
         </is>
@@ -10916,7 +10887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:EL75"/>
+  <dimension ref="A1:EL14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="6">
@@ -10925,707 +10896,707 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="V1" s="9" t="inlineStr">
+      <c r="V1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W1" s="9" t="inlineStr">
+      <c r="W1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="X1" s="11" t="inlineStr">
+      <c r="X1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AD1" s="10" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AE1" s="10" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AF1" s="12" t="inlineStr">
+      <c r="AF1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AG1" s="12" t="inlineStr">
+      <c r="AG1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AH1" s="12" t="inlineStr">
+      <c r="AH1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AI1" s="11" t="inlineStr">
+      <c r="AI1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AJ1" s="11" t="inlineStr">
+      <c r="AJ1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AK1" s="11" t="inlineStr">
+      <c r="AK1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AL1" s="12" t="inlineStr">
+      <c r="AL1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AM1" s="12" t="inlineStr">
+      <c r="AM1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AN1" s="12" t="inlineStr">
+      <c r="AN1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AO1" s="10" t="inlineStr">
+      <c r="AO1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AP1" s="10" t="inlineStr">
+      <c r="AP1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AR1" s="11" t="inlineStr">
+      <c r="AR1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AS1" s="10" t="inlineStr">
+      <c r="AS1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AU1" s="10" t="inlineStr">
+      <c r="AU1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AV1" s="10" t="inlineStr">
+      <c r="AV1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AW1" s="10" t="inlineStr">
+      <c r="AW1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AX1" s="10" t="inlineStr">
+      <c r="AX1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="AY1" s="11" t="inlineStr">
+      <c r="AY1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AZ1" s="11" t="inlineStr">
+      <c r="AZ1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BA1" s="11" t="inlineStr">
+      <c r="BA1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BB1" s="12" t="inlineStr">
+      <c r="BB1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BC1" s="12" t="inlineStr">
+      <c r="BC1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BD1" s="10" t="inlineStr">
+      <c r="BD1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="BE1" s="10" t="inlineStr">
+      <c r="BE1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="BF1" s="11" t="inlineStr">
+      <c r="BF1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BG1" s="11" t="inlineStr">
+      <c r="BG1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BH1" s="10" t="inlineStr">
+      <c r="BH1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="BI1" s="10" t="inlineStr">
+      <c r="BI1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="BJ1" s="11" t="inlineStr">
+      <c r="BJ1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BK1" s="11" t="inlineStr">
+      <c r="BK1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BL1" s="11" t="inlineStr">
+      <c r="BL1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BM1" s="11" t="inlineStr">
+      <c r="BM1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BN1" s="11" t="inlineStr">
+      <c r="BN1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BO1" s="12" t="inlineStr">
+      <c r="BO1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BP1" s="12" t="inlineStr">
+      <c r="BP1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BQ1" s="11" t="inlineStr">
+      <c r="BQ1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BR1" s="12" t="inlineStr">
+      <c r="BR1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BS1" s="9" t="inlineStr">
+      <c r="BS1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="BT1" s="9" t="inlineStr">
+      <c r="BT1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="BU1" s="12" t="inlineStr">
+      <c r="BU1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BV1" s="11" t="inlineStr">
+      <c r="BV1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BW1" s="11" t="inlineStr">
+      <c r="BW1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BX1" s="11" t="inlineStr">
+      <c r="BX1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BY1" s="12" t="inlineStr">
+      <c r="BY1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BZ1" s="12" t="inlineStr">
+      <c r="BZ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CA1" s="12" t="inlineStr">
+      <c r="CA1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CB1" s="12" t="inlineStr">
+      <c r="CB1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CC1" s="12" t="inlineStr">
+      <c r="CC1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CD1" s="12" t="inlineStr">
+      <c r="CD1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CE1" s="12" t="inlineStr">
+      <c r="CE1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CF1" s="12" t="inlineStr">
+      <c r="CF1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CG1" s="12" t="inlineStr">
+      <c r="CG1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CH1" s="12" t="inlineStr">
+      <c r="CH1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CI1" s="12" t="inlineStr">
+      <c r="CI1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CJ1" s="12" t="inlineStr">
+      <c r="CJ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CK1" s="12" t="inlineStr">
+      <c r="CK1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CL1" s="12" t="inlineStr">
+      <c r="CL1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CM1" s="12" t="inlineStr">
+      <c r="CM1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CN1" s="12" t="inlineStr">
+      <c r="CN1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CO1" s="12" t="inlineStr">
+      <c r="CO1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CP1" s="12" t="inlineStr">
+      <c r="CP1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CQ1" s="12" t="inlineStr">
+      <c r="CQ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CR1" s="12" t="inlineStr">
+      <c r="CR1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CS1" s="12" t="inlineStr">
+      <c r="CS1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CT1" s="12" t="inlineStr">
+      <c r="CT1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CU1" s="12" t="inlineStr">
+      <c r="CU1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CV1" s="12" t="inlineStr">
+      <c r="CV1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CW1" s="12" t="inlineStr">
+      <c r="CW1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CX1" s="12" t="inlineStr">
+      <c r="CX1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CY1" s="12" t="inlineStr">
+      <c r="CY1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="CZ1" s="12" t="inlineStr">
+      <c r="CZ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DA1" s="12" t="inlineStr">
+      <c r="DA1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DB1" s="12" t="inlineStr">
+      <c r="DB1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DC1" s="12" t="inlineStr">
+      <c r="DC1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DD1" s="12" t="inlineStr">
+      <c r="DD1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DE1" s="12" t="inlineStr">
+      <c r="DE1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DF1" s="12" t="inlineStr">
+      <c r="DF1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DG1" s="12" t="inlineStr">
+      <c r="DG1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DH1" s="12" t="inlineStr">
+      <c r="DH1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DI1" s="12" t="inlineStr">
+      <c r="DI1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DJ1" s="12" t="inlineStr">
+      <c r="DJ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DK1" s="12" t="inlineStr">
+      <c r="DK1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DL1" s="12" t="inlineStr">
+      <c r="DL1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DM1" s="12" t="inlineStr">
+      <c r="DM1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DN1" s="12" t="inlineStr">
+      <c r="DN1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DO1" s="12" t="inlineStr">
+      <c r="DO1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DP1" s="12" t="inlineStr">
+      <c r="DP1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DQ1" s="12" t="inlineStr">
+      <c r="DQ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DR1" s="12" t="inlineStr">
+      <c r="DR1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DS1" s="12" t="inlineStr">
+      <c r="DS1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DT1" s="12" t="inlineStr">
+      <c r="DT1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DU1" s="12" t="inlineStr">
+      <c r="DU1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DV1" s="12" t="inlineStr">
+      <c r="DV1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DW1" s="12" t="inlineStr">
+      <c r="DW1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DX1" s="12" t="inlineStr">
+      <c r="DX1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DY1" s="12" t="inlineStr">
+      <c r="DY1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="DZ1" s="12" t="inlineStr">
+      <c r="DZ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EA1" s="12" t="inlineStr">
+      <c r="EA1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EB1" s="12" t="inlineStr">
+      <c r="EB1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EC1" s="12" t="inlineStr">
+      <c r="EC1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="ED1" s="12" t="inlineStr">
+      <c r="ED1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EE1" s="12" t="inlineStr">
+      <c r="EE1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EF1" s="12" t="inlineStr">
+      <c r="EF1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EG1" s="12" t="inlineStr">
+      <c r="EG1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EH1" s="12" t="inlineStr">
+      <c r="EH1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EI1" s="12" t="inlineStr">
+      <c r="EI1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EJ1" s="12" t="inlineStr">
+      <c r="EJ1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EK1" s="12" t="inlineStr">
+      <c r="EK1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="EL1" s="12" t="inlineStr">
+      <c r="EL1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -12344,723 +12315,718 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>samp_name</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>samp_category</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>neg_cont_type</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>materialSampleID</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>sample_derived_from</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>sample_composed_of</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>rel_cont_id</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>biological_rep_relation</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>decimalLongitude</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>decimalLatitude</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>verbatimLongitude</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>verbatimLatitude</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>verbatimCoordinateSystem</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>verbatimSRS</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>eventDate</t>
         </is>
       </c>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr">
         <is>
           <t>eventDurationValue</t>
         </is>
       </c>
-      <c r="S3" s="13" t="inlineStr">
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>verbatimEventDate</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>verbatimEventTime</t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="V3" s="13" t="inlineStr">
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="W3" s="13" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="X3" s="13" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>habitat_natural_artificial_0_1</t>
         </is>
       </c>
-      <c r="Y3" s="13" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="Z3" s="13" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>samp_collect_device</t>
         </is>
       </c>
-      <c r="AA3" s="13" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>samp_size</t>
         </is>
       </c>
-      <c r="AB3" s="13" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>samp_size_unit</t>
         </is>
       </c>
-      <c r="AC3" s="13" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="AD3" s="13" t="inlineStr">
+      <c r="AD3" s="12" t="inlineStr">
         <is>
           <t>samp_store_sol</t>
         </is>
       </c>
-      <c r="AE3" s="13" t="inlineStr">
+      <c r="AE3" s="12" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="AF3" s="13" t="inlineStr">
+      <c r="AF3" s="12" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="AG3" s="13" t="inlineStr">
+      <c r="AG3" s="12" t="inlineStr">
         <is>
           <t>dna_store_loc</t>
         </is>
       </c>
-      <c r="AH3" s="13" t="inlineStr">
+      <c r="AH3" s="12" t="inlineStr">
         <is>
           <t>samp_store_method_additional</t>
         </is>
       </c>
-      <c r="AI3" s="13" t="inlineStr">
+      <c r="AI3" s="12" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AJ3" s="13" t="inlineStr">
+      <c r="AJ3" s="12" t="inlineStr">
         <is>
           <t>filter_passive_active_0_1</t>
         </is>
       </c>
-      <c r="AK3" s="13" t="inlineStr">
+      <c r="AK3" s="12" t="inlineStr">
         <is>
           <t>stationed_sample_dur</t>
         </is>
       </c>
-      <c r="AL3" s="13" t="inlineStr">
+      <c r="AL3" s="12" t="inlineStr">
         <is>
           <t>pump_flow_rate</t>
         </is>
       </c>
-      <c r="AM3" s="13" t="inlineStr">
+      <c r="AM3" s="12" t="inlineStr">
         <is>
           <t>pump_flow_rate_unit</t>
         </is>
       </c>
-      <c r="AN3" s="13" t="inlineStr">
+      <c r="AN3" s="12" t="inlineStr">
         <is>
           <t>prefilter_material</t>
         </is>
       </c>
-      <c r="AO3" s="13" t="inlineStr">
+      <c r="AO3" s="12" t="inlineStr">
         <is>
           <t>size_frac_low</t>
         </is>
       </c>
-      <c r="AP3" s="13" t="inlineStr">
+      <c r="AP3" s="12" t="inlineStr">
         <is>
           <t>size_frac</t>
         </is>
       </c>
-      <c r="AQ3" s="13" t="inlineStr">
+      <c r="AQ3" s="12" t="inlineStr">
         <is>
           <t>filter_diameter</t>
         </is>
       </c>
-      <c r="AR3" s="13" t="inlineStr">
+      <c r="AR3" s="12" t="inlineStr">
         <is>
           <t>filter_surface_area</t>
         </is>
       </c>
-      <c r="AS3" s="13" t="inlineStr">
+      <c r="AS3" s="12" t="inlineStr">
         <is>
           <t>filter_material</t>
         </is>
       </c>
-      <c r="AT3" s="13" t="inlineStr">
+      <c r="AT3" s="12" t="inlineStr">
         <is>
           <t>filter_name</t>
         </is>
       </c>
-      <c r="AU3" s="13" t="inlineStr">
+      <c r="AU3" s="12" t="inlineStr">
         <is>
           <t>precip_chem_prep</t>
         </is>
       </c>
-      <c r="AV3" s="13" t="inlineStr">
+      <c r="AV3" s="12" t="inlineStr">
         <is>
           <t>precip_force_prep</t>
         </is>
       </c>
-      <c r="AW3" s="13" t="inlineStr">
+      <c r="AW3" s="12" t="inlineStr">
         <is>
           <t>precip_time_prep</t>
         </is>
       </c>
-      <c r="AX3" s="13" t="inlineStr">
+      <c r="AX3" s="12" t="inlineStr">
         <is>
           <t>precip_temp_prep</t>
         </is>
       </c>
-      <c r="AY3" s="13" t="inlineStr">
+      <c r="AY3" s="12" t="inlineStr">
         <is>
           <t>prepped_samp_store_temp</t>
         </is>
       </c>
-      <c r="AZ3" s="13" t="inlineStr">
+      <c r="AZ3" s="12" t="inlineStr">
         <is>
           <t>prepped_samp_store_sol</t>
         </is>
       </c>
-      <c r="BA3" s="13" t="inlineStr">
+      <c r="BA3" s="12" t="inlineStr">
         <is>
           <t>prepped_samp_store_dur</t>
         </is>
       </c>
-      <c r="BB3" s="13" t="inlineStr">
+      <c r="BB3" s="12" t="inlineStr">
         <is>
           <t>prep_method_additional</t>
         </is>
       </c>
-      <c r="BC3" s="13" t="inlineStr">
+      <c r="BC3" s="12" t="inlineStr">
         <is>
           <t>date_ext</t>
         </is>
       </c>
-      <c r="BD3" s="13" t="inlineStr">
+      <c r="BD3" s="12" t="inlineStr">
         <is>
           <t>samp_vol_we_dna_ext</t>
         </is>
       </c>
-      <c r="BE3" s="13" t="inlineStr">
+      <c r="BE3" s="12" t="inlineStr">
         <is>
           <t>samp_vol_we_dna_ext_unit</t>
         </is>
       </c>
-      <c r="BF3" s="13" t="inlineStr">
+      <c r="BF3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext_lysis</t>
         </is>
       </c>
-      <c r="BG3" s="13" t="inlineStr">
+      <c r="BG3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext_sep</t>
         </is>
       </c>
-      <c r="BH3" s="13" t="inlineStr">
+      <c r="BH3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext</t>
         </is>
       </c>
-      <c r="BI3" s="13" t="inlineStr">
+      <c r="BI3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext_kit</t>
         </is>
       </c>
-      <c r="BJ3" s="13" t="inlineStr">
+      <c r="BJ3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext_modify</t>
         </is>
       </c>
-      <c r="BK3" s="13" t="inlineStr">
+      <c r="BK3" s="12" t="inlineStr">
         <is>
           <t>dna_cleanup_0_1</t>
         </is>
       </c>
-      <c r="BL3" s="13" t="inlineStr">
+      <c r="BL3" s="12" t="inlineStr">
         <is>
           <t>dna_cleanup_method</t>
         </is>
       </c>
-      <c r="BM3" s="13" t="inlineStr">
+      <c r="BM3" s="12" t="inlineStr">
         <is>
           <t>concentration</t>
         </is>
       </c>
-      <c r="BN3" s="13" t="inlineStr">
+      <c r="BN3" s="12" t="inlineStr">
         <is>
           <t>concentration_unit</t>
         </is>
       </c>
-      <c r="BO3" s="13" t="inlineStr">
+      <c r="BO3" s="12" t="inlineStr">
         <is>
           <t>concentration_method</t>
         </is>
       </c>
-      <c r="BP3" s="13" t="inlineStr">
+      <c r="BP3" s="12" t="inlineStr">
         <is>
           <t>ratioOfAbsorbance260_280</t>
         </is>
       </c>
-      <c r="BQ3" s="13" t="inlineStr">
+      <c r="BQ3" s="12" t="inlineStr">
         <is>
           <t>pool_dna_num</t>
         </is>
       </c>
-      <c r="BR3" s="13" t="inlineStr">
+      <c r="BR3" s="12" t="inlineStr">
         <is>
           <t>nucl_acid_ext_method_additional</t>
         </is>
       </c>
-      <c r="BS3" s="13" t="inlineStr">
+      <c r="BS3" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
-      <c r="BT3" s="13" t="inlineStr">
+      <c r="BT3" s="12" t="inlineStr">
         <is>
           <t>detected_notDetected</t>
         </is>
       </c>
-      <c r="BU3" s="13" t="inlineStr">
+      <c r="BU3" s="12" t="inlineStr">
         <is>
           <t>samp_weather</t>
         </is>
       </c>
-      <c r="BV3" s="13" t="inlineStr">
+      <c r="BV3" s="12" t="inlineStr">
         <is>
           <t>minimumDepthInMeters</t>
         </is>
       </c>
-      <c r="BW3" s="13" t="inlineStr">
+      <c r="BW3" s="12" t="inlineStr">
         <is>
           <t>maximumDepthInMeters</t>
         </is>
       </c>
-      <c r="BX3" s="13" t="inlineStr">
+      <c r="BX3" s="12" t="inlineStr">
         <is>
           <t>tot_depth_water_col</t>
         </is>
       </c>
-      <c r="BY3" s="13" t="inlineStr">
+      <c r="BY3" s="12" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BZ3" s="13" t="inlineStr">
+      <c r="BZ3" s="12" t="inlineStr">
         <is>
           <t>alt</t>
         </is>
       </c>
-      <c r="CA3" s="13" t="inlineStr">
+      <c r="CA3" s="12" t="inlineStr">
         <is>
           <t>temp</t>
         </is>
       </c>
-      <c r="CB3" s="13" t="inlineStr">
+      <c r="CB3" s="12" t="inlineStr">
         <is>
           <t>chlorophyll</t>
         </is>
       </c>
-      <c r="CC3" s="13" t="inlineStr">
+      <c r="CC3" s="12" t="inlineStr">
         <is>
           <t>light_intensity</t>
         </is>
       </c>
-      <c r="CD3" s="13" t="inlineStr">
+      <c r="CD3" s="12" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="CE3" s="13" t="inlineStr">
+      <c r="CE3" s="12" t="inlineStr">
         <is>
           <t>ph_meth</t>
         </is>
       </c>
-      <c r="CF3" s="13" t="inlineStr">
+      <c r="CF3" s="12" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="CG3" s="13" t="inlineStr">
+      <c r="CG3" s="12" t="inlineStr">
         <is>
           <t>suspend_part_matter</t>
         </is>
       </c>
-      <c r="CH3" s="13" t="inlineStr">
+      <c r="CH3" s="12" t="inlineStr">
         <is>
           <t>tidal_stage</t>
         </is>
       </c>
-      <c r="CI3" s="13" t="inlineStr">
+      <c r="CI3" s="12" t="inlineStr">
         <is>
           <t>turbidity</t>
         </is>
       </c>
-      <c r="CJ3" s="13" t="inlineStr">
+      <c r="CJ3" s="12" t="inlineStr">
         <is>
           <t>water_current</t>
         </is>
       </c>
-      <c r="CK3" s="13" t="inlineStr">
+      <c r="CK3" s="12" t="inlineStr">
         <is>
           <t>humidity</t>
         </is>
       </c>
-      <c r="CL3" s="13" t="inlineStr">
+      <c r="CL3" s="12" t="inlineStr">
         <is>
           <t>solar_irradiance</t>
         </is>
       </c>
-      <c r="CM3" s="13" t="inlineStr">
+      <c r="CM3" s="12" t="inlineStr">
         <is>
           <t>wind_direction</t>
         </is>
       </c>
-      <c r="CN3" s="13" t="inlineStr">
+      <c r="CN3" s="12" t="inlineStr">
         <is>
           <t>wind_speed</t>
         </is>
       </c>
-      <c r="CO3" s="13" t="inlineStr">
+      <c r="CO3" s="12" t="inlineStr">
         <is>
           <t>host_species</t>
         </is>
       </c>
-      <c r="CP3" s="13" t="inlineStr">
+      <c r="CP3" s="12" t="inlineStr">
         <is>
           <t>host_life_stage</t>
         </is>
       </c>
-      <c r="CQ3" s="13" t="inlineStr">
+      <c r="CQ3" s="12" t="inlineStr">
         <is>
           <t>host_tot_mass</t>
         </is>
       </c>
-      <c r="CR3" s="13" t="inlineStr">
+      <c r="CR3" s="12" t="inlineStr">
         <is>
           <t>host_tot_mass_unit</t>
         </is>
       </c>
-      <c r="CS3" s="13" t="inlineStr">
+      <c r="CS3" s="12" t="inlineStr">
         <is>
           <t>host_height</t>
         </is>
       </c>
-      <c r="CT3" s="13" t="inlineStr">
+      <c r="CT3" s="12" t="inlineStr">
         <is>
           <t>host_height_unit</t>
         </is>
       </c>
-      <c r="CU3" s="13" t="inlineStr">
+      <c r="CU3" s="12" t="inlineStr">
         <is>
           <t>host_length</t>
         </is>
       </c>
-      <c r="CV3" s="13" t="inlineStr">
+      <c r="CV3" s="12" t="inlineStr">
         <is>
           <t>host_length_unit</t>
         </is>
       </c>
-      <c r="CW3" s="13" t="inlineStr">
+      <c r="CW3" s="12" t="inlineStr">
         <is>
           <t>diss_inorg_carb</t>
         </is>
       </c>
-      <c r="CX3" s="13" t="inlineStr">
+      <c r="CX3" s="12" t="inlineStr">
         <is>
           <t>diss_inorg_carb_unit</t>
         </is>
       </c>
-      <c r="CY3" s="13" t="inlineStr">
+      <c r="CY3" s="12" t="inlineStr">
         <is>
           <t>diss_inorg_nitro</t>
         </is>
       </c>
-      <c r="CZ3" s="13" t="inlineStr">
+      <c r="CZ3" s="12" t="inlineStr">
         <is>
           <t>diss_inorg_nitro_unit</t>
         </is>
       </c>
-      <c r="DA3" s="13" t="inlineStr">
+      <c r="DA3" s="12" t="inlineStr">
         <is>
           <t>diss_org_carb</t>
         </is>
       </c>
-      <c r="DB3" s="13" t="inlineStr">
+      <c r="DB3" s="12" t="inlineStr">
         <is>
           <t>diss_org_carb_unit</t>
         </is>
       </c>
-      <c r="DC3" s="13" t="inlineStr">
+      <c r="DC3" s="12" t="inlineStr">
         <is>
           <t>diss_org_nitro</t>
         </is>
       </c>
-      <c r="DD3" s="13" t="inlineStr">
+      <c r="DD3" s="12" t="inlineStr">
         <is>
           <t>diss_org_nitro_unit</t>
         </is>
       </c>
-      <c r="DE3" s="13" t="inlineStr">
+      <c r="DE3" s="12" t="inlineStr">
         <is>
           <t>diss_oxygen</t>
         </is>
       </c>
-      <c r="DF3" s="13" t="inlineStr">
+      <c r="DF3" s="12" t="inlineStr">
         <is>
           <t>diss_oxygen_unit</t>
         </is>
       </c>
-      <c r="DG3" s="13" t="inlineStr">
+      <c r="DG3" s="12" t="inlineStr">
         <is>
           <t>tot_diss_nitro</t>
         </is>
       </c>
-      <c r="DH3" s="13" t="inlineStr">
+      <c r="DH3" s="12" t="inlineStr">
         <is>
           <t>tot_diss_nitro_unit</t>
         </is>
       </c>
-      <c r="DI3" s="13" t="inlineStr">
+      <c r="DI3" s="12" t="inlineStr">
         <is>
           <t>tot_inorg_nitro</t>
         </is>
       </c>
-      <c r="DJ3" s="13" t="inlineStr">
+      <c r="DJ3" s="12" t="inlineStr">
         <is>
           <t>tot_inorg_nitro_unit</t>
         </is>
       </c>
-      <c r="DK3" s="13" t="inlineStr">
+      <c r="DK3" s="12" t="inlineStr">
         <is>
           <t>tot_nitro</t>
         </is>
       </c>
-      <c r="DL3" s="13" t="inlineStr">
+      <c r="DL3" s="12" t="inlineStr">
         <is>
           <t>tot_nitro_unit</t>
         </is>
       </c>
-      <c r="DM3" s="13" t="inlineStr">
+      <c r="DM3" s="12" t="inlineStr">
         <is>
           <t>tot_part_carb</t>
         </is>
       </c>
-      <c r="DN3" s="13" t="inlineStr">
+      <c r="DN3" s="12" t="inlineStr">
         <is>
           <t>tot_part_carb_unit</t>
         </is>
       </c>
-      <c r="DO3" s="13" t="inlineStr">
+      <c r="DO3" s="12" t="inlineStr">
         <is>
           <t>tot_org_carb</t>
         </is>
       </c>
-      <c r="DP3" s="13" t="inlineStr">
+      <c r="DP3" s="12" t="inlineStr">
         <is>
           <t>tot_org_carb_unit</t>
         </is>
       </c>
-      <c r="DQ3" s="13" t="inlineStr">
+      <c r="DQ3" s="12" t="inlineStr">
         <is>
           <t>tot_org_c_meth</t>
         </is>
       </c>
-      <c r="DR3" s="13" t="inlineStr">
+      <c r="DR3" s="12" t="inlineStr">
         <is>
           <t>tot_nitro_content</t>
         </is>
       </c>
-      <c r="DS3" s="13" t="inlineStr">
+      <c r="DS3" s="12" t="inlineStr">
         <is>
           <t>tot_nitro_content_unit</t>
         </is>
       </c>
-      <c r="DT3" s="13" t="inlineStr">
+      <c r="DT3" s="12" t="inlineStr">
         <is>
           <t>tot_nitro_cont_meth</t>
         </is>
       </c>
-      <c r="DU3" s="13" t="inlineStr">
+      <c r="DU3" s="12" t="inlineStr">
         <is>
           <t>tot_carb</t>
         </is>
       </c>
-      <c r="DV3" s="13" t="inlineStr">
+      <c r="DV3" s="12" t="inlineStr">
         <is>
           <t>tot_carb_unit</t>
         </is>
       </c>
-      <c r="DW3" s="13" t="inlineStr">
+      <c r="DW3" s="12" t="inlineStr">
         <is>
           <t>part_org_carb</t>
         </is>
       </c>
-      <c r="DX3" s="13" t="inlineStr">
+      <c r="DX3" s="12" t="inlineStr">
         <is>
           <t>part_org_carb_unit</t>
         </is>
       </c>
-      <c r="DY3" s="13" t="inlineStr">
+      <c r="DY3" s="12" t="inlineStr">
         <is>
           <t>part_org_nitro</t>
         </is>
       </c>
-      <c r="DZ3" s="13" t="inlineStr">
+      <c r="DZ3" s="12" t="inlineStr">
         <is>
           <t>part_org_nitro_unit</t>
         </is>
       </c>
-      <c r="EA3" s="13" t="inlineStr">
+      <c r="EA3" s="12" t="inlineStr">
         <is>
           <t>nitrate</t>
         </is>
       </c>
-      <c r="EB3" s="13" t="inlineStr">
+      <c r="EB3" s="12" t="inlineStr">
         <is>
           <t>nitrate_unit</t>
         </is>
       </c>
-      <c r="EC3" s="13" t="inlineStr">
+      <c r="EC3" s="12" t="inlineStr">
         <is>
           <t>nitrite</t>
         </is>
       </c>
-      <c r="ED3" s="13" t="inlineStr">
+      <c r="ED3" s="12" t="inlineStr">
         <is>
           <t>nitrite_unit</t>
         </is>
       </c>
-      <c r="EE3" s="13" t="inlineStr">
+      <c r="EE3" s="12" t="inlineStr">
         <is>
           <t>nitro</t>
         </is>
       </c>
-      <c r="EF3" s="13" t="inlineStr">
+      <c r="EF3" s="12" t="inlineStr">
         <is>
           <t>nitro_unit</t>
         </is>
       </c>
-      <c r="EG3" s="13" t="inlineStr">
+      <c r="EG3" s="12" t="inlineStr">
         <is>
           <t>org_carb</t>
         </is>
       </c>
-      <c r="EH3" s="13" t="inlineStr">
+      <c r="EH3" s="12" t="inlineStr">
         <is>
           <t>org_carb_unit</t>
         </is>
       </c>
-      <c r="EI3" s="13" t="inlineStr">
+      <c r="EI3" s="12" t="inlineStr">
         <is>
           <t>org_matter</t>
         </is>
       </c>
-      <c r="EJ3" s="13" t="inlineStr">
+      <c r="EJ3" s="12" t="inlineStr">
         <is>
           <t>org_matter_unit</t>
         </is>
       </c>
-      <c r="EK3" s="13" t="inlineStr">
+      <c r="EK3" s="12" t="inlineStr">
         <is>
           <t>org_nitro</t>
         </is>
       </c>
-      <c r="EL3" s="13" t="inlineStr">
+      <c r="EL3" s="12" t="inlineStr">
         <is>
           <t>org_nitro_unit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ESL079</t>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>sample</t>
@@ -13068,2439 +13034,260 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
+          <t>United States, Dickinson, Iowa</t>
         </is>
       </c>
       <c r="BV4" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV5" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV6" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV7" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV8" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV9" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV10" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX10" t="n">
         <v>12</v>
       </c>
-      <c r="BW4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ESL078</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="BY10" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV5" t="n">
-        <v>33</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ESL077</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV11" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV6" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>51</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ESL076</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV12" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV7" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ESL075</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>United States, Dickinson, Iowa</t>
+        </is>
+      </c>
+      <c r="BV13" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV8" t="n">
-        <v>74</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>74</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ESL074</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV9" t="n">
-        <v>110</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>110</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ESL073</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV10" t="n">
-        <v>124</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>124</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ESL072</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV11" t="n">
-        <v>176</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>176</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ESL071</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV12" t="n">
-        <v>210</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>210</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ESL069</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV13" t="n">
-        <v>258</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>258</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ESL068</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
+          <t>United States, Dickinson, Iowa</t>
         </is>
       </c>
       <c r="BV14" t="n">
-        <v>280</v>
+        <v>-2147483648</v>
       </c>
       <c r="BW14" t="n">
-        <v>280</v>
+        <v>-2147483648</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.7</v>
+        <v>133</v>
       </c>
       <c r="BY14" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ESL067</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV15" t="n">
-        <v>298</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>298</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ESL066</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV16" t="n">
-        <v>308</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>308</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ESL065</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV17" t="n">
-        <v>322</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>322</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ESL064</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV18" t="n">
-        <v>330</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>330</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ESL063</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV19" t="n">
-        <v>340</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>340</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ESL062</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV20" t="n">
-        <v>346</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>346</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ESL061</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV21" t="n">
-        <v>356</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>356</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ESL059</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV22" t="n">
-        <v>368</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>368</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ESL058</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV23" t="n">
-        <v>380</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>380</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ESL057</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV24" t="n">
-        <v>419</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>419</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ESL056</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV25" t="n">
-        <v>457</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>457</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ESL055</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV26" t="n">
-        <v>467</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>467</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ESL054</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV27" t="n">
-        <v>479</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>479</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ESL053</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV28" t="n">
-        <v>491</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>491</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ESL052</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV29" t="n">
-        <v>507</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>507</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ESL051</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV30" t="n">
-        <v>547</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>547</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ESL049</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV31" t="n">
-        <v>566</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>566</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ESL048</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV32" t="n">
-        <v>590</v>
-      </c>
-      <c r="BW32" t="n">
-        <v>590</v>
-      </c>
-      <c r="BX32" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY32" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ESL047</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV33" t="n">
-        <v>635</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>635</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ESL046</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV34" t="n">
-        <v>670</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>670</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ESL045</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV35" t="n">
-        <v>717</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>717</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ESL044</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV36" t="n">
-        <v>728</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>728</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ESL043</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV37" t="n">
-        <v>739</v>
-      </c>
-      <c r="BW37" t="n">
-        <v>739</v>
-      </c>
-      <c r="BX37" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY37" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ESL042</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV38" t="n">
-        <v>758</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>758</v>
-      </c>
-      <c r="BX38" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY38" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ESL041</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV39" t="n">
-        <v>784</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>784</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ESL039</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV40" t="n">
-        <v>805</v>
-      </c>
-      <c r="BW40" t="n">
-        <v>805</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ESL038</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV41" t="n">
-        <v>821</v>
-      </c>
-      <c r="BW41" t="n">
-        <v>821</v>
-      </c>
-      <c r="BX41" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY41" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ESL037</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV42" t="n">
-        <v>829</v>
-      </c>
-      <c r="BW42" t="n">
-        <v>829</v>
-      </c>
-      <c r="BX42" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY42" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ESL036</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV43" t="n">
-        <v>841</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>841</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ESL035</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV44" t="n">
-        <v>850</v>
-      </c>
-      <c r="BW44" t="n">
-        <v>850</v>
-      </c>
-      <c r="BX44" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY44" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ESL034</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV45" t="n">
-        <v>860</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>860</v>
-      </c>
-      <c r="BX45" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ESL033</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV46" t="n">
-        <v>870</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>870</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ESL032</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV47" t="n">
-        <v>878</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>878</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ESL031</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV48" t="n">
-        <v>895</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>895</v>
-      </c>
-      <c r="BX48" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY48" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ESL029</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV49" t="n">
-        <v>905</v>
-      </c>
-      <c r="BW49" t="n">
-        <v>905</v>
-      </c>
-      <c r="BX49" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY49" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ESL028</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV50" t="n">
-        <v>917</v>
-      </c>
-      <c r="BW50" t="n">
-        <v>917</v>
-      </c>
-      <c r="BX50" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY50" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ESL027</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV51" t="n">
-        <v>934</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>934</v>
-      </c>
-      <c r="BX51" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY51" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ESL026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV52" t="n">
-        <v>973</v>
-      </c>
-      <c r="BW52" t="n">
-        <v>973</v>
-      </c>
-      <c r="BX52" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY52" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ESL025</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV53" t="n">
-        <v>993</v>
-      </c>
-      <c r="BW53" t="n">
-        <v>993</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ESL024</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV54" t="n">
-        <v>1012</v>
-      </c>
-      <c r="BW54" t="n">
-        <v>1012</v>
-      </c>
-      <c r="BX54" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY54" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ESL023</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV55" t="n">
-        <v>1053</v>
-      </c>
-      <c r="BW55" t="n">
-        <v>1053</v>
-      </c>
-      <c r="BX55" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY55" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>ESL022</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV56" t="n">
-        <v>1085</v>
-      </c>
-      <c r="BW56" t="n">
-        <v>1085</v>
-      </c>
-      <c r="BX56" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY56" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>ESL021</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV57" t="n">
-        <v>1113</v>
-      </c>
-      <c r="BW57" t="n">
-        <v>1113</v>
-      </c>
-      <c r="BX57" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY57" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>ESL019</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV58" t="n">
-        <v>1172</v>
-      </c>
-      <c r="BW58" t="n">
-        <v>1172</v>
-      </c>
-      <c r="BX58" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY58" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>ESL018</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV59" t="n">
-        <v>1201</v>
-      </c>
-      <c r="BW59" t="n">
-        <v>1201</v>
-      </c>
-      <c r="BX59" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY59" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ESL017</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV60" t="n">
-        <v>1235</v>
-      </c>
-      <c r="BW60" t="n">
-        <v>1235</v>
-      </c>
-      <c r="BX60" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY60" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ESL016</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV61" t="n">
-        <v>1252</v>
-      </c>
-      <c r="BW61" t="n">
-        <v>1252</v>
-      </c>
-      <c r="BX61" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY61" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ESL015</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV62" t="n">
-        <v>1282</v>
-      </c>
-      <c r="BW62" t="n">
-        <v>1282</v>
-      </c>
-      <c r="BX62" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY62" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ESL014</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV63" t="n">
-        <v>1315</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>1315</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ESL013</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV64" t="n">
-        <v>1351</v>
-      </c>
-      <c r="BW64" t="n">
-        <v>1351</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ESL012</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV65" t="n">
-        <v>1379</v>
-      </c>
-      <c r="BW65" t="n">
-        <v>1379</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>ESL011</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV66" t="n">
-        <v>1415</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>1415</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>ESL009</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV67" t="n">
-        <v>1463</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>1463</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ESL008</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV68" t="n">
-        <v>1534</v>
-      </c>
-      <c r="BW68" t="n">
-        <v>1534</v>
-      </c>
-      <c r="BX68" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY68" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>ESL007</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV69" t="n">
-        <v>1622</v>
-      </c>
-      <c r="BW69" t="n">
-        <v>1622</v>
-      </c>
-      <c r="BX69" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY69" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>ESL006</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV70" t="n">
-        <v>1648</v>
-      </c>
-      <c r="BW70" t="n">
-        <v>1648</v>
-      </c>
-      <c r="BX70" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY70" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>ESL005</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV71" t="n">
-        <v>1672</v>
-      </c>
-      <c r="BW71" t="n">
-        <v>1672</v>
-      </c>
-      <c r="BX71" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY71" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>ESL004</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV72" t="n">
-        <v>1692</v>
-      </c>
-      <c r="BW72" t="n">
-        <v>1692</v>
-      </c>
-      <c r="BX72" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY72" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ESL003</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV73" t="n">
-        <v>1708</v>
-      </c>
-      <c r="BW73" t="n">
-        <v>1708</v>
-      </c>
-      <c r="BX73" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY73" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>ESL002</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV74" t="n">
-        <v>1762</v>
-      </c>
-      <c r="BW74" t="n">
-        <v>1762</v>
-      </c>
-      <c r="BX74" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY74" t="n">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ESL001</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>China; Sichuan</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Niederreiter piston corer</t>
-        </is>
-      </c>
-      <c r="BV75" t="n">
-        <v>1777</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>1777</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>4165</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -15692,52 +13479,52 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -15801,57 +13588,57 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>samp_name</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>technical_rep_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>pcr_plate_id</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>quantificationCycle</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>rfu</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_method</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_unit</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_error</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_error_type</t>
         </is>
@@ -15894,57 +13681,57 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -16013,62 +13800,62 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>samp_name</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>technical_rep_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>pcr_plate_id</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>std_conc</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>std_conc_unit</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>quantificationCycle</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>rfu</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>efficiency</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>slope</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>intercept</t>
         </is>
@@ -16103,27 +13890,27 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -16162,32 +13949,32 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>num_detect</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_unit</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_error</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>estimatedNumberOfCopies_error_type</t>
         </is>
@@ -16226,97 +14013,97 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="O1" s="11" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -16425,102 +14212,102 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>samp_name</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>assay_name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>pcr_plate_id</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>lib_id</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>seq_run_id</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>lib_conc</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>lib_conc_unit</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>lib_conc_meth</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>phix_perc</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>mid_forward</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>mid_reverse</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>filename</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>filename2</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>checksum_filename</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>checksum_filename2</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>associatedSequences</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>input_read_count</t>
         </is>
       </c>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr">
         <is>
           <t>output_read_count</t>
         </is>
       </c>
-      <c r="S3" s="13" t="inlineStr">
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>output_otu_num</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>otu_num_tax_assigned</t>
         </is>
@@ -16555,102 +14342,102 @@
           <t># requirement_level_code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -16764,107 +14551,107 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>seq_id</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>dna_sequence</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>kingdom</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>phylum</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>family</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>genus</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>specificEpithet</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>scientificName</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>scientificNameAuthorship</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>taxonRank</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>taxonID</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>taxonID_db</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>verbatimIdentification</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>accession_id</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>accession_id_ref_db</t>
         </is>
       </c>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr">
         <is>
           <t>percent_match</t>
         </is>
       </c>
-      <c r="S3" s="13" t="inlineStr">
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>percent_query_cover</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>confidence_score</t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr">
         <is>
           <t>identificationRemarks</t>
         </is>
